--- a/DateBase/orders/Nha Thu_2026-9-1.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-1.xlsx
@@ -937,6 +937,9 @@
       <c r="G2" t="str">
         <v>051275661527612175102712310955157855105151510551511101010151051051015122520101010</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
